--- a/CAM 11/[CAM11] Reading_vocab.xlsx
+++ b/CAM 11/[CAM11] Reading_vocab.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03_English\7.0\IELTS_7.0\CAM 11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D071B714-620A-4F64-AC24-E6EF8F95890A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0E4D6F-AF47-490B-92E8-01C589D04781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test 1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="600">
   <si>
     <t>STT</t>
   </si>
@@ -68,1428 +68,16 @@
     <t>(v)</t>
   </si>
   <si>
-    <t>asthma</t>
-  </si>
-  <si>
-    <t>copper</t>
-  </si>
-  <si>
-    <t>manganese</t>
-  </si>
-  <si>
-    <t>arsenic</t>
-  </si>
-  <si>
-    <t>copper mine</t>
-  </si>
-  <si>
-    <t>miner</t>
-  </si>
-  <si>
-    <t>ketch</t>
-  </si>
-  <si>
-    <t>dredged</t>
-  </si>
-  <si>
-    <t>teething problem</t>
-  </si>
-  <si>
-    <t>sugar cube</t>
-  </si>
-  <si>
     <t>Từ vựng &amp; Từ đồng nghĩa</t>
   </si>
   <si>
-    <r>
-      <t>cater for</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= provide for)</t>
-    </r>
-  </si>
-  <si>
-    <t>Phục vụ, đáp ứng</t>
-  </si>
-  <si>
-    <t>To provide what is needed or wanted by a group.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The hotel tries to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>cater for</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> all exotic dietary needs.</t>
-    </r>
-  </si>
-  <si>
-    <t>Hen suyễn</t>
-  </si>
-  <si>
-    <t>A respiratory condition marked by spasms in the bronchi.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Air pollution can worsen the symptoms of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>asthma</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>so forth</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= and so on)</t>
-    </r>
-  </si>
-  <si>
-    <t>(idm)</t>
-  </si>
-  <si>
-    <t>Vân vân</t>
-  </si>
-  <si>
-    <t>Used to refer to other things of the type just mentioned.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">We discussed the budget, the timeline, and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>so forth</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>expertise</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= proficiency)</t>
-    </r>
-  </si>
-  <si>
-    <t>Chuyên môn</t>
-  </si>
-  <si>
-    <t>Expert skill or knowledge in a particular field.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Thomas has considerable </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>expertise</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> in Splunk development.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>publicise</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= promote)</t>
-    </r>
-  </si>
-  <si>
-    <t>Quảng bá</t>
-  </si>
-  <si>
-    <t>To make something widely known to the public.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The company needs to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>publicise</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> its new security features.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>cargo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= freight/goods)</t>
-    </r>
-  </si>
-  <si>
-    <t>Hàng hóa (vận tải)</t>
-  </si>
-  <si>
-    <t>Goods carried on a ship, aircraft, or motor vehicle.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The ship was carrying a heavy </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>cargo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> of iron ore.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>tremendous</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= huge/vast)</t>
-    </r>
-  </si>
-  <si>
-    <t>To lớn, kinh khủng</t>
-  </si>
-  <si>
-    <t>Very great in amount, scale, or intensity.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The internet has had a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tremendous</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> impact on education.</t>
-    </r>
-  </si>
-  <si>
-    <t>prospector</t>
-  </si>
-  <si>
-    <t>Người dò tìm mỏ</t>
-  </si>
-  <si>
-    <t>A person who searches for natural resources (gold, oil).</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the 1800s, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>prospectors</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> flocked to California for gold.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>smelted</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= melted)</t>
-    </r>
-  </si>
-  <si>
-    <t>Luyện kim</t>
-  </si>
-  <si>
-    <t>Extracted metal from its ore by a process involving heating.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Iron ore must be </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>smelted</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> before it can be used for steel.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>mined</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= extracted)</t>
-    </r>
-  </si>
-  <si>
-    <t>Được khai thác</t>
-  </si>
-  <si>
-    <t>Extracted from a mine.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Rare earth minerals are </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>mined</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> in several parts of Asia.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>emigrate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= migrate)</t>
-    </r>
-  </si>
-  <si>
-    <t>Di cư (ra nước ngoài)</t>
-  </si>
-  <si>
-    <t>To leave one's own country to settle permanently in another.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">His grandparents decided to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>emigrate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to Australia.</t>
-    </r>
-  </si>
-  <si>
-    <t>Nạo vét</t>
-  </si>
-  <si>
-    <t>To clear the bed of (a harbor/river) by scooping out mud.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The canal needs to be </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>dredged</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to allow larger ships.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>implication</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= consequence)</t>
-    </r>
-  </si>
-  <si>
-    <t>Hệ quả, ngụ ý</t>
-  </si>
-  <si>
-    <t>A likely consequence of an action or decision.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">What are the financial </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>implications</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> of this merger?</t>
-    </r>
-  </si>
-  <si>
     <t>(n phr)</t>
   </si>
   <si>
-    <t>Khó khăn ban đầu</t>
-  </si>
-  <si>
-    <t>Minor problems that happen when something starts.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Every new software has some </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>teething problems</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> at first.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>eventually</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= finally)</t>
-    </r>
-  </si>
-  <si>
     <t>(adv)</t>
   </si>
   <si>
-    <t>Cuối cùng thì</t>
-  </si>
-  <si>
-    <t>In the end, especially after a long delay or problem.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">We worked hard and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>eventually</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> finished the migration.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>halt to</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= stop)</t>
-    </r>
-  </si>
-  <si>
-    <t>Dừng lại</t>
-  </si>
-  <si>
-    <t>To bring an activity to a sudden or temporary stop.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The strike brought production to a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>halt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>pliable</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= flexible)</t>
-    </r>
-  </si>
-  <si>
-    <t>Dễ uốn, dẻo</t>
-  </si>
-  <si>
-    <t>Easy to bend; flexible.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quality leather should be </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>pliable</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> and soft.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>drastically</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= severely)</t>
-    </r>
-  </si>
-  <si>
-    <t>Một cách quyết liệt</t>
-  </si>
-  <si>
     <t>In a way that is likely to have a strong or far-reaching effect.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Prices have fallen </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>drastically</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> since the new law.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>lessen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= reduce/diminish)</t>
-    </r>
-  </si>
-  <si>
-    <t>Làm giảm bớt</t>
-  </si>
-  <si>
-    <t>To make or become less; diminish.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Regular exercise can help </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>lessen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> the risk of heart disease.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>speculation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= guesswork)</t>
-    </r>
-  </si>
-  <si>
-    <t>Sự suy đoán</t>
-  </si>
-  <si>
-    <t>The forming of a theory without firm evidence.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">There is much </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>speculation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> about the future of AI.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>eradication</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= elimination)</t>
-    </r>
-  </si>
-  <si>
-    <t>Sự xóa sổ</t>
-  </si>
-  <si>
-    <t>The complete destruction of something.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>eradication</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> of poverty is a global challenge.</t>
-    </r>
-  </si>
-  <si>
-    <t>Đồng</t>
-  </si>
-  <si>
-    <t>A reddish-brown metal that is a good conductor of heat and electricity.</t>
-  </si>
-  <si>
-    <r>
-      <t>Copper</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> is widely used in electrical wiring.</t>
-    </r>
-  </si>
-  <si>
-    <t>Mangan</t>
-  </si>
-  <si>
-    <t>A hard, brittle, silvery metal often used in making steel.</t>
-  </si>
-  <si>
-    <r>
-      <t>Manganese</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> is an essential element in industrial metal alloys.</t>
-    </r>
-  </si>
-  <si>
-    <t>Thạch tín</t>
-  </si>
-  <si>
-    <t>A brittle, steel-gray metalloid that is highly poisonous.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The soil was contaminated with high levels of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>arsenic</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>programme</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= plan/project)</t>
-    </r>
-  </si>
-  <si>
-    <t>Chương trình</t>
-  </si>
-  <si>
-    <t>A planned series of future events or performances.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The government launched a new health </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>programme</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> for children.</t>
-    </r>
-  </si>
-  <si>
-    <t>Mỏ đồng</t>
-  </si>
-  <si>
-    <t>A place where copper ore is extracted from the ground.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">He spent his whole life working in a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>copper mine</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Công nhân mỏ</t>
-  </si>
-  <si>
-    <t>A person who works in a mine.</t>
-  </si>
-  <si>
-    <r>
-      <t>Miners</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> often face dangerous conditions underground.</t>
-    </r>
-  </si>
-  <si>
-    <t>Thuyền buồm hai cột</t>
-  </si>
-  <si>
-    <t>A sailing boat with two masts, the smaller one being behind the main mast.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">They sailed across the bay in a traditional </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ketch</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>silt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= sediment)</t>
-    </r>
-  </si>
-  <si>
-    <t>Bùn/Phù sa</t>
-  </si>
-  <si>
-    <t>Fine sand, clay, or other material carried by running water.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The river mouth was blocked by a build-up of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>silt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>company brochure</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= booklet)</t>
-    </r>
-  </si>
-  <si>
-    <t>Cuốn sách giới thiệu công ty</t>
-  </si>
-  <si>
-    <t>A small book containing information about a company's services.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">You can find more details in our </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>company brochure</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>leaflet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= flyer/pamphlet)</t>
-    </r>
-  </si>
-  <si>
-    <t>Tờ rơi</t>
-  </si>
-  <si>
-    <t>A printed sheet of paper containing information or advertising.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">They were handing out </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>leaflets</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> about the new library.</t>
-    </r>
-  </si>
-  <si>
-    <t>nano-particle</t>
-  </si>
-  <si>
-    <t>Hạt nano</t>
-  </si>
-  <si>
-    <t>A microscopic particle whose size is measured in nanometres.</t>
-  </si>
-  <si>
-    <r>
-      <t>Nano-particles</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> are used in medicine to deliver drugs to specific cells.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>durable metal</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= sturdy metal)</t>
-    </r>
-  </si>
-  <si>
-    <t>Kim loại bền</t>
-  </si>
-  <si>
-    <t>Metal that is able to withstand wear, pressure, or damage.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Titanium is known as a very </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>durable metal</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>shrink computer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= downsize)</t>
-    </r>
-  </si>
-  <si>
-    <t>Thu nhỏ máy tính</t>
-  </si>
-  <si>
-    <t>To make computers smaller in size using technology.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The goal is to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>shrink computers</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to the size of a credit card.</t>
-    </r>
-  </si>
-  <si>
-    <t>Viên đường</t>
-  </si>
-  <si>
-    <t>A small cube of granulated sugar.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">A supercomputer might one day be smaller than a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>sugar cube</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>contaminant</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= pollutant)</t>
-    </r>
-  </si>
-  <si>
-    <t>Chất gây ô nhiễm</t>
-  </si>
-  <si>
-    <t>A substance that makes something impure or harmful.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Filters are used to remove </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>contaminants</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> from the water.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -4706,6 +3294,2406 @@
   </si>
   <si>
     <t>Column1</t>
+  </si>
+  <si>
+    <t>A ship or large boat.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Among the English </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>vessels</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> was a warship by the name of Mary Rose.</t>
+    </r>
+  </si>
+  <si>
+    <t>A report or description of an event or experience.</t>
+  </si>
+  <si>
+    <r>
+      <t>Accounts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> of what happened to the ship vary among different witnesses.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>overladen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= overloaded)</t>
+    </r>
+  </si>
+  <si>
+    <t>Quá tải</t>
+  </si>
+  <si>
+    <t>Loaded with too many things or people.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Some maintain that the ship was </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>overladen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and sailing too low in the water.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Others believe the ship was </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mishandled</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by an undisciplined crew.</t>
+    </r>
+  </si>
+  <si>
+    <t>Không thể bàn cãi</t>
+  </si>
+  <si>
+    <t>That cannot be questioned or proved to be false.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">What is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>undisputed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> is that the Mary Rose sank into the Solent that day.</t>
+    </r>
+  </si>
+  <si>
+    <t>starboard</t>
+  </si>
+  <si>
+    <t>Mạn phải (tàu)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The ship came to rest on the seabed, lying on her </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>starboard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> side.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The exposed port side was </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>eroded</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by marine organisms.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The ship's hull suffered from mechanical </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>degradation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> over time.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>intact</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= undamaged)</t>
+    </r>
+  </si>
+  <si>
+    <t>Nguyên vẹn</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nearly all of the starboard half of the ship survived </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>intact</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fishermen found that their equipment was caught on an underwater </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>obstruction</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sunken</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= submerged)</t>
+    </r>
+  </si>
+  <si>
+    <t>Bị chìm</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The diver was exploring another </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sunken</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ship nearby.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">He found the equipment caught on a timber </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>protruding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> slightly from the seabed.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>timber</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= wood)</t>
+    </r>
+  </si>
+  <si>
+    <t>Wood that is prepared for use in building.</t>
+  </si>
+  <si>
+    <t>bronze</t>
+  </si>
+  <si>
+    <t>Đồng thiếc</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The divers uncovered several timbers and a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>bronze</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> gun.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deane continued diving on the site </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>intermittently</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> until 1840.</t>
+    </r>
+  </si>
+  <si>
+    <t>The state of being unknown, inconspicuous, or unimportant.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The Mary Rose then faded into </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>obscurity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> for another hundred years.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>wreck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= shipwreck)</t>
+    </r>
+  </si>
+  <si>
+    <t>Xác tàu chìm</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The project was a plan to examine a number of known </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>wrecks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in the Solent.</t>
+    </r>
+  </si>
+  <si>
+    <t>To become involved in a particular situation or activity.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">McKee </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>entered into</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> collaboration with an electrical engineering professor.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sự khai quật</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Further </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>excavations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> revealed stray pieces of timber and an iron gun.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>climax</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= peak)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>climax</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to the operation came when part of the ship's frame was uncovered.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kho tàng</t>
+  </si>
+  <si>
+    <t>A store of valuable or delightful things.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The wreck housed a treasure </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>trove</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> of beautifully preserved artefacts.</t>
+    </r>
+  </si>
+  <si>
+    <t>Hiện vật</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thousands of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>artefacts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> were recovered from the Mary Rose site.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kích thủy lực</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The suction problem was overcome by using 12 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hydraulic jacks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The hull was transferred underwater into the lifting </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>cradle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bản vẽ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The cradle was designed using archaeological survey </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>drawings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>vessel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= ship)</t>
+    </r>
+  </si>
+  <si>
+    <t>Tàu, thuyền lớn</t>
+  </si>
+  <si>
+    <r>
+      <t>account of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= report)</t>
+    </r>
+  </si>
+  <si>
+    <t>Bản tường thuật, lời kể</t>
+  </si>
+  <si>
+    <t>mishandled</t>
+  </si>
+  <si>
+    <t>Xử lý sai, điều khiển tồi</t>
+  </si>
+  <si>
+    <t>To manage or deal with something wrongly or ineffectively.</t>
+  </si>
+  <si>
+    <t>The side of a ship that is on the right when facing forward.</t>
+  </si>
+  <si>
+    <t>to be eroded</t>
+  </si>
+  <si>
+    <t>Bị xói mòn, ăn mòn</t>
+  </si>
+  <si>
+    <t>To be gradually destroyed by natural forces.</t>
+  </si>
+  <si>
+    <t>degradation</t>
+  </si>
+  <si>
+    <t>Sự suy thoái, phân hủy</t>
+  </si>
+  <si>
+    <t>The process of being damaged or made worse.</t>
+  </si>
+  <si>
+    <t>Not damaged or destroyed; complete.</t>
+  </si>
+  <si>
+    <r>
+      <t>obstruction</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= barrier)</t>
+    </r>
+  </si>
+  <si>
+    <t>Vật cản</t>
+  </si>
+  <si>
+    <t>Something that blocks a road, an entrance, or a path.</t>
+  </si>
+  <si>
+    <t>Having sunk to the bottom of a body of water.</t>
+  </si>
+  <si>
+    <r>
+      <t>protruding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= sticking out)</t>
+    </r>
+  </si>
+  <si>
+    <t>Nhô ra, trồi lên</t>
+  </si>
+  <si>
+    <t>Sticking out from or through something.</t>
+  </si>
+  <si>
+    <t>Gỗ xây dựng</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">He found the equipment caught on a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>timber</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> protruding slightly from the seabed.</t>
+    </r>
+  </si>
+  <si>
+    <t>A yellowish-brown alloy of copper and tin.</t>
+  </si>
+  <si>
+    <t>intermittently</t>
+  </si>
+  <si>
+    <t>Định kỳ, không liên tục</t>
+  </si>
+  <si>
+    <t>At irregular intervals; not continuously or steadily.</t>
+  </si>
+  <si>
+    <t>obscurity</t>
+  </si>
+  <si>
+    <t>Sự mờ nhạt, lãng quên</t>
+  </si>
+  <si>
+    <t>The remains of a ship that has been destroyed or sunk.</t>
+  </si>
+  <si>
+    <t>entered into</t>
+  </si>
+  <si>
+    <t>Tham gia vào, bắt đầu</t>
+  </si>
+  <si>
+    <t>excavation</t>
+  </si>
+  <si>
+    <t>The action of digging in the ground to look for old objects.</t>
+  </si>
+  <si>
+    <t>Đỉnh điểm, cao trào</t>
+  </si>
+  <si>
+    <t>The most exciting or important part of something.</t>
+  </si>
+  <si>
+    <t>trove</t>
+  </si>
+  <si>
+    <t>artefact</t>
+  </si>
+  <si>
+    <t>An object made by a human being, typically of historical interest.</t>
+  </si>
+  <si>
+    <t>hydraulic jacks</t>
+  </si>
+  <si>
+    <t>Devices used to lift heavy loads using liquid pressure.</t>
+  </si>
+  <si>
+    <t>cradle</t>
+  </si>
+  <si>
+    <t>Khung nâng</t>
+  </si>
+  <si>
+    <t>A frame used to support something, especially a ship.</t>
+  </si>
+  <si>
+    <r>
+      <t>drawing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= sketch)</t>
+    </r>
+  </si>
+  <si>
+    <t>A picture or diagram made with a pencil or pen.</t>
+  </si>
+  <si>
+    <t>undisputed</t>
+  </si>
+  <si>
+    <t>ethnographer</t>
+  </si>
+  <si>
+    <t>Nhà dân tộc học</t>
+  </si>
+  <si>
+    <t>A person who studies different societies and cultures.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The Norwegian </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ethnographer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Thor Heyerdahl believed the settlers came from South America.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>statue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= sculpture)</t>
+    </r>
+  </si>
+  <si>
+    <t>Bức tượng</t>
+  </si>
+  <si>
+    <t>A figure of a person or animal in stone, metal, or wood.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The island is famous for its massive stone </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>statues</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, known as moai.</t>
+    </r>
+  </si>
+  <si>
+    <t>genetic</t>
+  </si>
+  <si>
+    <t>Thuộc di truyền</t>
+  </si>
+  <si>
+    <t>Relating to genes or heredity.</t>
+  </si>
+  <si>
+    <r>
+      <t>Genetic</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> evidence later proved that the islanders were actually from Polynesia.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>folklore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= mythology)</t>
+    </r>
+  </si>
+  <si>
+    <t>Văn hóa dân gian</t>
+  </si>
+  <si>
+    <t>The traditional beliefs and stories of a community passed by word of mouth.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Local </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>folklore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tells stories of how the great statues "walked" to their sites.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>scrawny</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= skinny/thin)</t>
+    </r>
+  </si>
+  <si>
+    <t>Gầy gò/Khẳng khiu</t>
+  </si>
+  <si>
+    <t>(Of a person or animal) unsafely thin and bony.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Only a few </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>scrawny</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> trees were left on the island when Europeans arrived.</t>
+    </r>
+  </si>
+  <si>
+    <t>pollen</t>
+  </si>
+  <si>
+    <t>Phấn hoa</t>
+  </si>
+  <si>
+    <t>A fine powder produced by flowers, which is carried by the wind or insects.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Scientists studied </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>pollen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> preserved in lake sediments to understand the past.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sediment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= deposit)</t>
+    </r>
+  </si>
+  <si>
+    <t>Trầm tích/Cặn</t>
+  </si>
+  <si>
+    <t>Matter that settles to the bottom of a liquid.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The lake </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sediments</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> contained evidence of a once-lush palm forest.</t>
+    </r>
+  </si>
+  <si>
+    <t>palm</t>
+  </si>
+  <si>
+    <t>Cây cọ/Cây dừa</t>
+  </si>
+  <si>
+    <t>A tropical tree with a straight trunk and a mass of long leaves at the top.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The island was once covered with millions of giant </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>palm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> trees.</t>
+    </r>
+  </si>
+  <si>
+    <t>descended</t>
+  </si>
+  <si>
+    <t>Xuất thân/Bắt nguồn</t>
+  </si>
+  <si>
+    <t>To be related to a particular person or group who lived in the past.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The modern islanders are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>descended</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> from Polynesian navigators.</t>
+    </r>
+  </si>
+  <si>
+    <t>cannibalism</t>
+  </si>
+  <si>
+    <t>Tục ăn thịt người</t>
+  </si>
+  <si>
+    <t>The practice of eating the flesh of one's own species.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Some theories suggest that food shortages led to war and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>cannibalism</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>rival chieftains</t>
+  </si>
+  <si>
+    <t>Các thủ lĩnh đối địch</t>
+  </si>
+  <si>
+    <t>Leaders of different tribes who are in competition or conflict.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The island was divided into territories ruled by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>rival chieftains</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>sledge</t>
+  </si>
+  <si>
+    <t>Xe trượt</t>
+  </si>
+  <si>
+    <t>A vehicle on runners for conveying loads or passengers over snow or ice.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">One theory is that the statues were moved on wooden </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sledges</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>hauled</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= dragged)</t>
+    </r>
+  </si>
+  <si>
+    <t>Kéo mạnh/Vận chuyển</t>
+  </si>
+  <si>
+    <t>To pull or drag something with great effort.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The heavy stones were </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hauled</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> across the island using ropes and manpower.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>toppling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= knocking over)</t>
+    </r>
+  </si>
+  <si>
+    <t>Làm đổ/Lật đổ</t>
+  </si>
+  <si>
+    <t>Overbalancing or causing to fall over.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Many statues were found </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>toppling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> over after a period of civil unrest.</t>
+    </r>
+  </si>
+  <si>
+    <t>wind-lashed</t>
+  </si>
+  <si>
+    <t>Bị gió quật mạnh</t>
+  </si>
+  <si>
+    <t>Hit or beaten repeatedly by strong winds.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The island's </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>wind-lashed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> environment made farming difficult.</t>
+    </r>
+  </si>
+  <si>
+    <t>infertile fields</t>
+  </si>
+  <si>
+    <t>Cánh đồng cằn cỗi</t>
+  </si>
+  <si>
+    <t>Land that is not capable of producing many crops.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Over-farming and deforestation turned the land into </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>infertile fields</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>circular stone</t>
+  </si>
+  <si>
+    <t>Vòng đá/Đá tròn</t>
+  </si>
+  <si>
+    <t>A stone or arrangement of stones in a circle.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Islanders built </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>circular stone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> windbreaks to protect their crops.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>contend</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= assert/claim)</t>
+    </r>
+  </si>
+  <si>
+    <t>Cho rằng/Tranh luận</t>
+  </si>
+  <si>
+    <t>To assert something as a position in an argument.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Some researchers </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>contend</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> that rats, not humans, destroyed the forest.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>settler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= colonist)</t>
+    </r>
+  </si>
+  <si>
+    <t>Người định cư</t>
+  </si>
+  <si>
+    <t>A person who goes to live in a new place where few people lived before.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The first </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>settlers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> brought chickens and crops to the island.</t>
+    </r>
+  </si>
+  <si>
+    <t>immunity</t>
+  </si>
+  <si>
+    <t>Sự miễn dịch</t>
+  </si>
+  <si>
+    <t>The ability of an organism to resist a particular infection or toxin.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The islanders had no </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>immunity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to the diseases brought by foreigners.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>decimate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= destroy)</t>
+    </r>
+  </si>
+  <si>
+    <t>Tàn sát/Hủy diệt</t>
+  </si>
+  <si>
+    <t>To kill, destroy, or remove a large percentage of a population.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Foreign diseases began to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>decimate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> the local population in the 1800s.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>shrivelled</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= withered)</t>
+    </r>
+  </si>
+  <si>
+    <t>Co lại/Héo hon</t>
+  </si>
+  <si>
+    <t>Wrinkled and contracted, especially due to loss of moisture or old age.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The once-great civilization became a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>shrivelled</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> version of its former self.</t>
+    </r>
+  </si>
+  <si>
+    <t>neuroaesthetics</t>
+  </si>
+  <si>
+    <t>Mỹ học thần kinh</t>
+  </si>
+  <si>
+    <t>amygdala</t>
+  </si>
+  <si>
+    <t>Hạch hạnh nhân</t>
+  </si>
+  <si>
+    <t>The scientific study of the neural bases for the creation of art.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The discipline of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>neuroaesthetics</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> brings objectivity to the study of art.</t>
+    </r>
+  </si>
+  <si>
+    <t>A part of the brain involved with experiencing emotions.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>amygdala</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> lights up when we look at certain paintings.</t>
+    </r>
+  </si>
+  <si>
+    <t>geometrical</t>
+  </si>
+  <si>
+    <t>Thuộc hình học</t>
+  </si>
+  <si>
+    <t>Relating to geometry, or the use of straight lines and shapes.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mondrian’s works are known for their strict </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>geometrical</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> shapes.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>haphazard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= random)</t>
+    </r>
+  </si>
+  <si>
+    <t>Ngẫu nhiên/Bừa bãi</t>
+  </si>
+  <si>
+    <t>Lacking any obvious principle of organization.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">People can distinguish a masterpiece from a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>haphazard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> splash of paint.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>inclination to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= tendency)</t>
+    </r>
+  </si>
+  <si>
+    <t>Khuynh hướng</t>
+  </si>
+  <si>
+    <t>A person's natural tendency or urge to act in a certain way.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We have a natural </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>inclination to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> find certain patterns more pleasing.</t>
+    </r>
+  </si>
+  <si>
+    <t>the doodles of infants</t>
+  </si>
+  <si>
+    <t>Nét vẽ nguệch ngoạc</t>
+  </si>
+  <si>
+    <t>Simple drawings or scribbles made by very young children.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Volunteers compared famous paintings with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>the doodles of infants</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>chimps</t>
+  </si>
+  <si>
+    <t>Con tinh tinh</t>
+  </si>
+  <si>
+    <t>Short for chimpanzees, a species of great ape.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The study compared human art with paintings made by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>chimps</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>messy brushstrokes</t>
+  </si>
+  <si>
+    <t>Nét cọ lộn xộn</t>
+  </si>
+  <si>
+    <t>Untidy or careless marks made with a paintbrush.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Even in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>messy brushstrokes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, there is often an underlying sense of order.</t>
+    </r>
+  </si>
+  <si>
+    <t>representational</t>
+  </si>
+  <si>
+    <t>Miêu tả thực tế</t>
+  </si>
+  <si>
+    <t>Seeking to depict the physical appearance of things.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We find it easier to decipher </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>representational</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> art than abstract art.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>decipher</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= decode)</t>
+    </r>
+  </si>
+  <si>
+    <t>Giải mã/Hiểu</t>
+  </si>
+  <si>
+    <t>To succeed in understanding or identifying something.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Our brains try to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>decipher</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> the shapes and colors we see in a painting.</t>
+    </r>
+  </si>
+  <si>
+    <t>meticulously composed</t>
+  </si>
+  <si>
+    <t>Bố cục tỉ mỉ</t>
+  </si>
+  <si>
+    <t>Carefully and precisely arranged or organized.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Though they look simple, Mondrian's works are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>meticulously composed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>flit across</t>
+  </si>
+  <si>
+    <t>Lướt qua/Vụt qua</t>
+  </si>
+  <si>
+    <t>To move quickly and lightly across something.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Our eyes </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>flit across</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> a canvas, searching for recognizable patterns.</t>
+    </r>
+  </si>
+  <si>
+    <t>interpretation</t>
+  </si>
+  <si>
+    <t>Sự giải thích/Diễn giải</t>
+  </si>
+  <si>
+    <t>The action of explaining the meaning of something.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Abstract art leaves more room for personal </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>interpretation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>intricacy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= complexity)</t>
+    </r>
+  </si>
+  <si>
+    <t>Sự phức tạp/Tỉ mỉ</t>
+  </si>
+  <si>
+    <t>The quality of being very detailed or complex.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>intricacy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> of a design can hold our attention for a long time.</t>
+    </r>
+  </si>
+  <si>
+    <t>perceptual overload</t>
+  </si>
+  <si>
+    <t>Quá tải nhận thức</t>
+  </si>
+  <si>
+    <t>A state where the senses are overwhelmed by too much info.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Too much complexity in a painting can lead to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>perceptual overload</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>fractals</t>
+  </si>
+  <si>
+    <t>Phân hình</t>
+  </si>
+  <si>
+    <t>Geometric figures where each part has the same character as the whole.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pollock’s paintings show the same self-similarity of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>fractals</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>motifs</t>
+  </si>
+  <si>
+    <t>Họa tiết/Chủ đề</t>
+  </si>
+  <si>
+    <t>A distinctive feature or dominant idea in an artistic composition.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The brain is programmed to recognize certain </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>motifs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in art.</t>
+    </r>
+  </si>
+  <si>
+    <t>linger</t>
+  </si>
+  <si>
+    <t>Nán lại/Đọng lại</t>
+  </si>
+  <si>
+    <t>To stay in a place longer than necessary.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Our eyes tend to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>linger</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> on images that follow certain mathematical rules.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -4873,7 +5861,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
@@ -4881,23 +5869,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4950,48 +5923,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="33">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="medium">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -5201,9 +6151,9 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
+        <top style="medium">
           <color rgb="FF000000"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -5218,26 +6168,42 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="medium">
+        <bottom style="medium">
           <color rgb="FF000000"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color rgb="FF000000"/>
         </left>
         <right style="medium">
           <color rgb="FF000000"/>
         </right>
-        <top style="medium">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -5446,46 +6412,10 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="medium">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="medium">
           <color rgb="FF000000"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -5505,6 +6435,13 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5521,7 +6458,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color rgb="FF000000"/>
@@ -5532,6 +6469,9 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -5748,13 +6688,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FF000000"/>
         </left>
@@ -5767,6 +6700,42 @@
         <bottom style="medium">
           <color rgb="FF000000"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="medium">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -5783,16 +6752,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E478E778-151F-42EC-9614-DE27854E3EBC}" name="Table1" displayName="Table1" ref="A1:G21" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="32" tableBorderDxfId="33" totalsRowBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E478E778-151F-42EC-9614-DE27854E3EBC}" name="Table1" displayName="Table1" ref="A1:G21" totalsRowShown="0" headerRowDxfId="32" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A1:G21" xr:uid="{E478E778-151F-42EC-9614-DE27854E3EBC}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{91CBC9E2-3B19-48A1-A88C-4347542743B8}" name="STT" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{B292EE0A-8B23-4DE4-ADBF-F27F07FC681C}" name="Từ vựng &amp; Từ đồng nghĩa" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{2B1FDE52-ABC7-4070-8867-F5F44F2831EC}" name="Loại từ" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{B840BB9A-4E60-495C-8620-9187CCA67B2A}" name="Nghĩa tiếng Việt" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{9652B0E6-084E-4595-9BF3-4E61E224A4F5}" name="Định nghĩa tiếng Anh" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{1BD3E985-93C2-4B31-881F-DAA30BADB693}" name="Ví dụ" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{CD952651-A299-4A41-A8ED-0DF96DFA9FCD}" name="Column1" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{91CBC9E2-3B19-48A1-A88C-4347542743B8}" name="STT" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{B292EE0A-8B23-4DE4-ADBF-F27F07FC681C}" name="Từ vựng &amp; Từ đồng nghĩa" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{2B1FDE52-ABC7-4070-8867-F5F44F2831EC}" name="Loại từ" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{B840BB9A-4E60-495C-8620-9187CCA67B2A}" name="Nghĩa tiếng Việt" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{9652B0E6-084E-4595-9BF3-4E61E224A4F5}" name="Định nghĩa tiếng Anh" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{1BD3E985-93C2-4B31-881F-DAA30BADB693}" name="Ví dụ" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{CD952651-A299-4A41-A8ED-0DF96DFA9FCD}" name="Column1" dataDxfId="22">
       <calculatedColumnFormula>"#" &amp; D2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5801,16 +6770,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{70B436F1-60E0-47E6-AEDA-60D46CCB3976}" name="Table2" displayName="Table2" ref="A23:G52" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="22" tableBorderDxfId="23" totalsRowBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{70B436F1-60E0-47E6-AEDA-60D46CCB3976}" name="Table2" displayName="Table2" ref="A23:G52" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A23:G52" xr:uid="{70B436F1-60E0-47E6-AEDA-60D46CCB3976}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{93BA2D32-E486-4505-93D3-BF91AE3EBE82}" name="STT" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{0C5A083D-D465-4A71-B223-70A886C9D37F}" name="Từ vựng &amp; Từ đồng nghĩa" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{2F929016-02CB-4B0B-94A0-8F551ADF7C6A}" name="Loại từ" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{47FC0640-B7D7-4E3D-AD66-52F742181F61}" name="Nghĩa tiếng Việt" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{340AA3E4-0E73-4F6B-BD20-49D501D9DEA6}" name="Định nghĩa tiếng Anh" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{4EDE12CC-7921-4AE6-91E6-8435BB3EF147}" name="Ví dụ" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{A055A0C4-70CA-4566-B5E0-57198B9E6F83}" name="Column1" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{93BA2D32-E486-4505-93D3-BF91AE3EBE82}" name="STT" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{0C5A083D-D465-4A71-B223-70A886C9D37F}" name="Từ vựng &amp; Từ đồng nghĩa" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{2F929016-02CB-4B0B-94A0-8F551ADF7C6A}" name="Loại từ" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{47FC0640-B7D7-4E3D-AD66-52F742181F61}" name="Nghĩa tiếng Việt" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{340AA3E4-0E73-4F6B-BD20-49D501D9DEA6}" name="Định nghĩa tiếng Anh" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{4EDE12CC-7921-4AE6-91E6-8435BB3EF147}" name="Ví dụ" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{A055A0C4-70CA-4566-B5E0-57198B9E6F83}" name="Column1" dataDxfId="11">
       <calculatedColumnFormula>"#" &amp; D24</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5819,15 +6788,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2EA34561-F621-455B-B3A5-9B17AB6A3CD9}" name="Table3" displayName="Table3" ref="A54:G86" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2EA34561-F621-455B-B3A5-9B17AB6A3CD9}" name="Table3" displayName="Table3" ref="A54:G86" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A54:G86" xr:uid="{2EA34561-F621-455B-B3A5-9B17AB6A3CD9}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{096A2AAE-0C22-41A2-A7F2-C5E460139D06}" name="STT" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{A32C46C2-79E8-4123-81FB-04E6CA7803BF}" name="Từ vựng &amp; Từ đồng nghĩa" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{AACED9E9-D742-45CF-8FFC-A4B3D6FA9B57}" name="Loại từ" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{3B27B534-C921-4E5A-97CB-D58FD98C1228}" name="Nghĩa tiếng Việt" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{57A726C4-08D1-4991-8D83-9D2B0CE861D8}" name="Định nghĩa tiếng Anh" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{67597548-2E1E-409D-9A6A-B7D0F37C291C}" name="Ví dụ" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{096A2AAE-0C22-41A2-A7F2-C5E460139D06}" name="STT" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{A32C46C2-79E8-4123-81FB-04E6CA7803BF}" name="Từ vựng &amp; Từ đồng nghĩa" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{AACED9E9-D742-45CF-8FFC-A4B3D6FA9B57}" name="Loại từ" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{3B27B534-C921-4E5A-97CB-D58FD98C1228}" name="Nghĩa tiếng Việt" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{57A726C4-08D1-4991-8D83-9D2B0CE861D8}" name="Định nghĩa tiếng Anh" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{67597548-2E1E-409D-9A6A-B7D0F37C291C}" name="Ví dụ" dataDxfId="1"/>
     <tableColumn id="7" xr3:uid="{9EB9E6B8-2B35-4763-B485-D7781AD3AA29}" name="Column1" dataDxfId="0">
       <calculatedColumnFormula>"#" &amp; D54</calculatedColumnFormula>
     </tableColumn>
@@ -6112,46 +7081,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="14" t="s">
+      <c r="B1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>483</v>
+      <c r="G1" s="9" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>157</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>158</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>160</v>
+        <v>15</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="G2" t="str">
         <f t="shared" ref="G2:G21" si="0">"#" &amp; D2</f>
@@ -6159,23 +7128,23 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="10">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>161</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>164</v>
+        <v>19</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="G3" t="str">
         <f t="shared" si="0"/>
@@ -6183,23 +7152,23 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="10">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>166</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>167</v>
+        <v>12</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" si="0"/>
@@ -6207,23 +7176,23 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="10">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>168</v>
+        <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>169</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>171</v>
+        <v>26</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="G5" t="str">
         <f t="shared" si="0"/>
@@ -6231,23 +7200,23 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="10">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>172</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>173</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>175</v>
+        <v>30</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" si="0"/>
@@ -6255,23 +7224,23 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="10">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>177</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>179</v>
+        <v>34</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
@@ -6279,23 +7248,23 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="10">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>181</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>183</v>
+        <v>38</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="G8" t="str">
         <f t="shared" si="0"/>
@@ -6303,23 +7272,23 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="10">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>184</v>
+        <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>187</v>
+        <v>42</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" si="0"/>
@@ -6327,23 +7296,23 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="10">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>191</v>
+        <v>46</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" si="0"/>
@@ -6351,23 +7320,23 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>193</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>195</v>
+        <v>50</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" si="0"/>
@@ -6375,23 +7344,23 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>196</v>
+        <v>52</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>197</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>199</v>
+        <v>54</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" si="0"/>
@@ -6399,23 +7368,23 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="10">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>200</v>
+        <v>56</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>201</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>203</v>
+        <v>58</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="0"/>
@@ -6423,23 +7392,23 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="10">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>204</v>
+        <v>60</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>205</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>207</v>
+        <v>62</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" si="0"/>
@@ -6447,23 +7416,23 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="10">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>208</v>
+        <v>64</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>209</v>
+        <v>65</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>211</v>
+        <v>66</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" si="0"/>
@@ -6471,23 +7440,23 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="10">
+      <c r="A16" s="5">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>212</v>
+        <v>68</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>213</v>
+        <v>69</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>214</v>
+        <v>70</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>216</v>
+        <v>71</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" si="0"/>
@@ -6495,23 +7464,23 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="10">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>218</v>
+        <v>74</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>220</v>
+        <v>75</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" si="0"/>
@@ -6519,23 +7488,23 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="10">
+      <c r="A18" s="5">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>224</v>
+        <v>79</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" si="0"/>
@@ -6543,23 +7512,23 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="10">
+      <c r="A19" s="5">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>228</v>
+        <v>83</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="0"/>
@@ -6567,23 +7536,23 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="10">
+      <c r="A20" s="5">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>229</v>
+        <v>85</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>230</v>
+        <v>86</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>231</v>
+        <v>87</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>233</v>
+        <v>88</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" si="0"/>
@@ -6591,23 +7560,23 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="16">
+      <c r="A21" s="11">
         <v>20</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>237</v>
+      <c r="B21" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>93</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" si="0"/>
@@ -6615,46 +7584,46 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="21" t="s">
+      <c r="B23" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G23" s="21" t="s">
-        <v>483</v>
+      <c r="G23" s="16" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="10">
+      <c r="A24" s="5">
         <v>1</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>238</v>
+        <v>94</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>239</v>
+        <v>95</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>241</v>
+        <v>96</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" ref="G24:G52" si="1">"#" &amp; D24</f>
@@ -6662,23 +7631,23 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="10">
+      <c r="A25" s="5">
         <v>2</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>242</v>
+        <v>98</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>243</v>
+        <v>99</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>245</v>
+        <v>100</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="1"/>
@@ -6686,23 +7655,23 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="10">
+      <c r="A26" s="5">
         <v>3</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>246</v>
+        <v>102</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>247</v>
+        <v>103</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>249</v>
+        <v>104</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="G26" t="str">
         <f t="shared" si="1"/>
@@ -6710,23 +7679,23 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="10">
+      <c r="A27" s="5">
         <v>4</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>250</v>
+        <v>106</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>251</v>
+        <v>107</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>253</v>
+        <v>108</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="G27" t="str">
         <f t="shared" si="1"/>
@@ -6734,23 +7703,23 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="10">
+      <c r="A28" s="5">
         <v>5</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>254</v>
+        <v>110</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>255</v>
+        <v>111</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>257</v>
+        <v>112</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="G28" t="str">
         <f t="shared" si="1"/>
@@ -6758,23 +7727,23 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="10">
+      <c r="A29" s="5">
         <v>6</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>258</v>
+        <v>114</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>259</v>
+        <v>115</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>261</v>
+        <v>116</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="G29" t="str">
         <f t="shared" si="1"/>
@@ -6782,23 +7751,23 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="10">
+      <c r="A30" s="5">
         <v>7</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>262</v>
+        <v>118</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>263</v>
+        <v>119</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>265</v>
+        <v>120</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="G30" t="str">
         <f t="shared" si="1"/>
@@ -6806,23 +7775,23 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="10">
+      <c r="A31" s="5">
         <v>8</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>266</v>
+        <v>122</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>267</v>
+        <v>123</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>269</v>
+        <v>124</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="1"/>
@@ -6830,23 +7799,23 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="10">
+      <c r="A32" s="5">
         <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>270</v>
+        <v>126</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>271</v>
+        <v>127</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>273</v>
+        <v>128</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" si="1"/>
@@ -6854,23 +7823,23 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="10">
+      <c r="A33" s="5">
         <v>10</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>274</v>
+        <v>130</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>275</v>
+        <v>131</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>277</v>
+        <v>132</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="1"/>
@@ -6878,23 +7847,23 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="10">
+      <c r="A34" s="5">
         <v>11</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>278</v>
+        <v>134</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>279</v>
+        <v>135</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>281</v>
+        <v>136</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>137</v>
       </c>
       <c r="G34" t="str">
         <f t="shared" si="1"/>
@@ -6902,23 +7871,23 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="10">
+      <c r="A35" s="5">
         <v>12</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>282</v>
+        <v>138</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>283</v>
+        <v>139</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>285</v>
+        <v>140</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="G35" t="str">
         <f t="shared" si="1"/>
@@ -6926,23 +7895,23 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="10">
+      <c r="A36" s="5">
         <v>13</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>286</v>
+        <v>142</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>287</v>
+        <v>143</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>289</v>
+        <v>144</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="G36" t="str">
         <f t="shared" si="1"/>
@@ -6950,23 +7919,23 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="10">
+      <c r="A37" s="5">
         <v>14</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>290</v>
+        <v>146</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>213</v>
+        <v>69</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>291</v>
+        <v>147</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>293</v>
+        <v>148</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="G37" t="str">
         <f t="shared" si="1"/>
@@ -6974,23 +7943,23 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="10">
+      <c r="A38" s="5">
         <v>15</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>294</v>
+        <v>150</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>295</v>
+        <v>151</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>296</v>
+        <v>152</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>298</v>
+        <v>153</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>154</v>
       </c>
       <c r="G38" t="str">
         <f t="shared" si="1"/>
@@ -6998,23 +7967,23 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="10">
+      <c r="A39" s="5">
         <v>16</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>299</v>
+        <v>155</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>300</v>
+        <v>156</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>302</v>
+        <v>157</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>158</v>
       </c>
       <c r="G39" t="str">
         <f t="shared" si="1"/>
@@ -7022,23 +7991,23 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="10">
+      <c r="A40" s="5">
         <v>17</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>303</v>
+        <v>159</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>304</v>
+        <v>160</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>306</v>
+        <v>161</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="G40" t="str">
         <f t="shared" si="1"/>
@@ -7046,23 +8015,23 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="10">
+      <c r="A41" s="5">
         <v>18</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>307</v>
+        <v>163</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>308</v>
+        <v>164</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>310</v>
+        <v>165</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="G41" t="str">
         <f t="shared" si="1"/>
@@ -7070,23 +8039,23 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="10">
+      <c r="A42" s="5">
         <v>19</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>311</v>
+        <v>167</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>312</v>
+        <v>168</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>314</v>
+        <v>169</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="G42" t="str">
         <f t="shared" si="1"/>
@@ -7094,23 +8063,23 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="10">
+      <c r="A43" s="5">
         <v>20</v>
       </c>
-      <c r="B43" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="C43" s="18" t="s">
+      <c r="B43" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D43" s="17" t="s">
-        <v>316</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>318</v>
+      <c r="D43" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>174</v>
       </c>
       <c r="G43" t="str">
         <f t="shared" si="1"/>
@@ -7118,23 +8087,23 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="10">
+      <c r="A44" s="5">
         <v>21</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>319</v>
+        <v>175</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>320</v>
+        <v>176</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>346</v>
+        <v>177</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="G44" t="str">
         <f t="shared" si="1"/>
@@ -7142,23 +8111,23 @@
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="10">
+      <c r="A45" s="5">
         <v>22</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>322</v>
+        <v>178</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>323</v>
+        <v>179</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>347</v>
+        <v>180</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="G45" t="str">
         <f t="shared" si="1"/>
@@ -7166,23 +8135,23 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="10">
+      <c r="A46" s="5">
         <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>325</v>
+        <v>181</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>326</v>
+        <v>182</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>348</v>
+        <v>183</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>204</v>
       </c>
       <c r="G46" t="str">
         <f t="shared" si="1"/>
@@ -7190,23 +8159,23 @@
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="10">
+      <c r="A47" s="5">
         <v>24</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>328</v>
+        <v>184</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>329</v>
+        <v>185</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>349</v>
+        <v>186</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="G47" t="str">
         <f t="shared" si="1"/>
@@ -7214,23 +8183,23 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="10">
+      <c r="A48" s="5">
         <v>25</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>331</v>
+        <v>187</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>332</v>
+        <v>188</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>350</v>
+        <v>189</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>206</v>
       </c>
       <c r="G48" t="str">
         <f t="shared" si="1"/>
@@ -7238,23 +8207,23 @@
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="10">
+      <c r="A49" s="5">
         <v>26</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>334</v>
+        <v>190</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>335</v>
+        <v>191</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>351</v>
+        <v>192</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>207</v>
       </c>
       <c r="G49" t="str">
         <f t="shared" si="1"/>
@@ -7262,23 +8231,23 @@
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="10">
+      <c r="A50" s="5">
         <v>27</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>343</v>
+        <v>199</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>337</v>
+        <v>193</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>352</v>
+        <v>194</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="G50" t="str">
         <f t="shared" si="1"/>
@@ -7286,23 +8255,23 @@
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="10">
+      <c r="A51" s="5">
         <v>28</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>344</v>
+        <v>200</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>339</v>
+        <v>195</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>353</v>
+        <v>196</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="G51" t="str">
         <f t="shared" si="1"/>
@@ -7310,23 +8279,23 @@
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="10">
+      <c r="A52" s="5">
         <v>29</v>
       </c>
-      <c r="B52" s="17" t="s">
-        <v>345</v>
-      </c>
-      <c r="C52" s="18" t="s">
+      <c r="B52" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D52" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>354</v>
+      <c r="D52" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>210</v>
       </c>
       <c r="G52" t="str">
         <f t="shared" si="1"/>
@@ -7334,46 +8303,46 @@
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B54" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C54" s="24" t="s">
+      <c r="B54" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E54" s="24" t="s">
+      <c r="E54" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F54" s="25" t="s">
+      <c r="F54" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G54" s="24" t="s">
-        <v>483</v>
+      <c r="G54" s="19" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="10">
+      <c r="A55" s="5">
         <v>1</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>355</v>
+        <v>211</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>356</v>
+        <v>212</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>358</v>
+        <v>213</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="G55" t="str">
         <f t="shared" ref="G55:G86" si="2">"#" &amp; D54</f>
@@ -7381,23 +8350,23 @@
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="10">
+      <c r="A56" s="5">
         <v>2</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>359</v>
+        <v>215</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>360</v>
+        <v>216</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>362</v>
+        <v>217</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="G56" t="str">
         <f t="shared" si="2"/>
@@ -7405,23 +8374,23 @@
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="10">
+      <c r="A57" s="5">
         <v>3</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>363</v>
+        <v>219</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>364</v>
+        <v>220</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>366</v>
+        <v>221</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="G57" t="str">
         <f t="shared" si="2"/>
@@ -7429,23 +8398,23 @@
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="10">
+      <c r="A58" s="5">
         <v>4</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>367</v>
+        <v>223</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>368</v>
+        <v>224</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>370</v>
+        <v>225</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>226</v>
       </c>
       <c r="G58" t="str">
         <f t="shared" si="2"/>
@@ -7453,23 +8422,23 @@
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="10">
+      <c r="A59" s="5">
         <v>5</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>371</v>
+        <v>227</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>372</v>
+        <v>228</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>374</v>
+        <v>229</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>230</v>
       </c>
       <c r="G59" t="str">
         <f t="shared" si="2"/>
@@ -7477,23 +8446,23 @@
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="10">
+      <c r="A60" s="5">
         <v>6</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>375</v>
+        <v>231</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>376</v>
+        <v>232</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>378</v>
+        <v>233</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>234</v>
       </c>
       <c r="G60" t="str">
         <f t="shared" si="2"/>
@@ -7501,23 +8470,23 @@
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="10">
+      <c r="A61" s="5">
         <v>7</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>379</v>
+        <v>235</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>380</v>
+        <v>236</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>382</v>
+        <v>237</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>238</v>
       </c>
       <c r="G61" t="str">
         <f t="shared" si="2"/>
@@ -7525,23 +8494,23 @@
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="10">
+      <c r="A62" s="5">
         <v>8</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>383</v>
+        <v>239</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>384</v>
+        <v>240</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>386</v>
+        <v>241</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="G62" t="str">
         <f t="shared" si="2"/>
@@ -7549,23 +8518,23 @@
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="10">
+      <c r="A63" s="5">
         <v>9</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>387</v>
+        <v>243</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>388</v>
+        <v>244</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>390</v>
+        <v>245</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>246</v>
       </c>
       <c r="G63" t="str">
         <f t="shared" si="2"/>
@@ -7573,23 +8542,23 @@
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="10">
+      <c r="A64" s="5">
         <v>10</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>391</v>
+        <v>247</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>392</v>
+        <v>248</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>394</v>
+        <v>249</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>250</v>
       </c>
       <c r="G64" t="str">
         <f t="shared" si="2"/>
@@ -7597,23 +8566,23 @@
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="10">
+      <c r="A65" s="5">
         <v>11</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>395</v>
+        <v>251</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>396</v>
+        <v>252</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="F65" s="12" t="s">
-        <v>398</v>
+        <v>253</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>254</v>
       </c>
       <c r="G65" t="str">
         <f t="shared" si="2"/>
@@ -7621,23 +8590,23 @@
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="10">
+      <c r="A66" s="5">
         <v>12</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>399</v>
+        <v>255</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>400</v>
+        <v>256</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>402</v>
+        <v>257</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>258</v>
       </c>
       <c r="G66" t="str">
         <f t="shared" si="2"/>
@@ -7645,23 +8614,23 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="10">
+      <c r="A67" s="5">
         <v>13</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>403</v>
+        <v>259</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>404</v>
+        <v>260</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>406</v>
+        <v>261</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>262</v>
       </c>
       <c r="G67" t="str">
         <f t="shared" si="2"/>
@@ -7669,23 +8638,23 @@
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="10">
+      <c r="A68" s="5">
         <v>14</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>407</v>
+        <v>263</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>408</v>
+        <v>264</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F68" s="11" t="s">
-        <v>410</v>
+        <v>265</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>266</v>
       </c>
       <c r="G68" t="str">
         <f t="shared" si="2"/>
@@ -7693,23 +8662,23 @@
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="10">
+      <c r="A69" s="5">
         <v>15</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>411</v>
+        <v>267</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>412</v>
+        <v>268</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="F69" s="12" t="s">
-        <v>414</v>
+        <v>269</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>270</v>
       </c>
       <c r="G69" t="str">
         <f t="shared" si="2"/>
@@ -7717,23 +8686,23 @@
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="10">
+      <c r="A70" s="5">
         <v>16</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>415</v>
+        <v>271</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>416</v>
+        <v>272</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>418</v>
+        <v>273</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>274</v>
       </c>
       <c r="G70" t="str">
         <f t="shared" si="2"/>
@@ -7741,23 +8710,23 @@
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="10">
+      <c r="A71" s="5">
         <v>17</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>419</v>
+        <v>275</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>420</v>
+        <v>276</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="F71" s="12" t="s">
-        <v>422</v>
+        <v>277</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>278</v>
       </c>
       <c r="G71" t="str">
         <f t="shared" si="2"/>
@@ -7765,23 +8734,23 @@
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="10">
+      <c r="A72" s="5">
         <v>18</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>423</v>
+        <v>279</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>424</v>
+        <v>280</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>426</v>
+        <v>281</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>282</v>
       </c>
       <c r="G72" t="str">
         <f t="shared" si="2"/>
@@ -7789,23 +8758,23 @@
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="10">
+      <c r="A73" s="5">
         <v>19</v>
       </c>
-      <c r="B73" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="C73" s="18" t="s">
+      <c r="B73" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C73" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D73" s="17" t="s">
-        <v>428</v>
-      </c>
-      <c r="E73" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="F73" s="19" t="s">
-        <v>430</v>
+      <c r="D73" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="F73" s="14" t="s">
+        <v>286</v>
       </c>
       <c r="G73" t="str">
         <f t="shared" si="2"/>
@@ -7813,23 +8782,23 @@
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="10">
+      <c r="A74" s="5">
         <v>20</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>431</v>
+        <v>287</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>432</v>
+        <v>288</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>434</v>
+        <v>289</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>290</v>
       </c>
       <c r="G74" t="str">
         <f t="shared" si="2"/>
@@ -7837,23 +8806,23 @@
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="10">
+      <c r="A75" s="5">
         <v>21</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>435</v>
+        <v>291</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>436</v>
+        <v>292</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="F75" s="12" t="s">
-        <v>438</v>
+        <v>293</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="G75" t="str">
         <f t="shared" si="2"/>
@@ -7861,23 +8830,23 @@
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="10">
+      <c r="A76" s="5">
         <v>22</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>439</v>
+        <v>295</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>440</v>
+        <v>296</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="F76" s="12" t="s">
-        <v>442</v>
+        <v>297</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="G76" t="str">
         <f t="shared" si="2"/>
@@ -7885,23 +8854,23 @@
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="10">
+      <c r="A77" s="5">
         <v>23</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>443</v>
+        <v>299</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>444</v>
+        <v>300</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="F77" s="12" t="s">
-        <v>446</v>
+        <v>301</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>302</v>
       </c>
       <c r="G77" t="str">
         <f t="shared" si="2"/>
@@ -7909,23 +8878,23 @@
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="10">
+      <c r="A78" s="5">
         <v>24</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>447</v>
+        <v>303</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>448</v>
+        <v>304</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>450</v>
+        <v>305</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>306</v>
       </c>
       <c r="G78" t="str">
         <f t="shared" si="2"/>
@@ -7933,23 +8902,23 @@
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="10">
+      <c r="A79" s="5">
         <v>25</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>451</v>
+        <v>307</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>452</v>
+        <v>308</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F79" s="12" t="s">
-        <v>454</v>
+        <v>309</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>310</v>
       </c>
       <c r="G79" t="str">
         <f t="shared" si="2"/>
@@ -7957,23 +8926,23 @@
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="10">
+      <c r="A80" s="5">
         <v>26</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>455</v>
+        <v>311</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>456</v>
+        <v>312</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="F80" s="12" t="s">
-        <v>458</v>
+        <v>313</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>314</v>
       </c>
       <c r="G80" t="str">
         <f t="shared" si="2"/>
@@ -7981,23 +8950,23 @@
       </c>
     </row>
     <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="10">
+      <c r="A81" s="5">
         <v>27</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>459</v>
+        <v>315</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>460</v>
+        <v>316</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="F81" s="12" t="s">
-        <v>462</v>
+        <v>317</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>318</v>
       </c>
       <c r="G81" t="str">
         <f t="shared" si="2"/>
@@ -8005,23 +8974,23 @@
       </c>
     </row>
     <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="10">
+      <c r="A82" s="5">
         <v>28</v>
       </c>
-      <c r="B82" s="17" t="s">
-        <v>463</v>
-      </c>
-      <c r="C82" s="18" t="s">
+      <c r="B82" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C82" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D82" s="17" t="s">
-        <v>464</v>
-      </c>
-      <c r="E82" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="F82" s="19" t="s">
-        <v>466</v>
+      <c r="D82" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="F82" s="14" t="s">
+        <v>322</v>
       </c>
       <c r="G82" t="str">
         <f t="shared" si="2"/>
@@ -8029,23 +8998,23 @@
       </c>
     </row>
     <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="10">
+      <c r="A83" s="5">
         <v>29</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>467</v>
+        <v>323</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>468</v>
+        <v>324</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F83" s="12" t="s">
-        <v>470</v>
+        <v>325</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>326</v>
       </c>
       <c r="G83" t="str">
         <f t="shared" si="2"/>
@@ -8053,23 +9022,23 @@
       </c>
     </row>
     <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="10">
+      <c r="A84" s="5">
         <v>30</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>471</v>
+        <v>327</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>472</v>
+        <v>328</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="F84" s="12" t="s">
-        <v>474</v>
+        <v>329</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>330</v>
       </c>
       <c r="G84" t="str">
         <f t="shared" si="2"/>
@@ -8077,23 +9046,23 @@
       </c>
     </row>
     <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="10">
+      <c r="A85" s="5">
         <v>31</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>475</v>
+        <v>331</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>476</v>
+        <v>332</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>478</v>
+        <v>333</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>334</v>
       </c>
       <c r="G85" t="str">
         <f t="shared" si="2"/>
@@ -8101,23 +9070,23 @@
       </c>
     </row>
     <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="10">
+      <c r="A86" s="5">
         <v>32</v>
       </c>
-      <c r="B86" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="C86" s="18" t="s">
+      <c r="B86" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="C86" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D86" s="17" t="s">
-        <v>480</v>
-      </c>
-      <c r="E86" s="18" t="s">
-        <v>481</v>
-      </c>
-      <c r="F86" s="19" t="s">
-        <v>482</v>
+      <c r="D86" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="F86" s="14" t="s">
+        <v>338</v>
       </c>
       <c r="G86" t="str">
         <f t="shared" si="2"/>
@@ -8136,756 +9105,1684 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C4D416C-A01B-45FE-B15D-10C804210BEF}">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="7"/>
+    <col min="1" max="1" width="8.796875" style="3"/>
     <col min="2" max="2" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.796875" style="7"/>
-    <col min="4" max="4" width="24.8984375" style="9" customWidth="1"/>
-    <col min="5" max="5" width="64.19921875" style="9" customWidth="1"/>
-    <col min="6" max="6" width="61.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="3"/>
+    <col min="4" max="4" width="24.69921875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.8984375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="64.19921875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="61.09765625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="24">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="24" t="str">
+        <f>"#" &amp; E2</f>
+        <v>#Tàu, thuyền lớn</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="24">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="24" t="str">
+        <f t="shared" ref="D3:D26" si="0">"#" &amp; E3</f>
+        <v>#Bản tường thuật, lời kể</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="24">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Quá tải</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="24">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Xử lý sai, điều khiển tồi</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="24">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Mạn phải (tàu)</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="24">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Bị xói mòn, ăn mòn</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>402</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="24">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Sự suy thoái, phân hủy</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>405</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="24">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Nguyên vẹn</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="24">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Vật cản</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="24">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Bị chìm</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>410</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="24">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Nhô ra, trồi lên</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="24">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Gỗ xây dựng</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>366</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="24">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Đồng thiếc</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>416</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="24">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Định kỳ, không liên tục</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>419</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="24">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Sự mờ nhạt, lãng quên</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>371</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="24">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Xác tàu chìm</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>422</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="24">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Tham gia vào, bắt đầu</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>376</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="24">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Sự khai quật</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>426</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="24">
         <v>19</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="B20" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Đỉnh điểm, cao trào</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>428</v>
+      </c>
+      <c r="G20" s="24" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="24">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Kho tàng</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="24">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Hiện vật</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>431</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="24">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Kích thủy lực</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>433</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Khung nâng</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="24">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Bản vẽ</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>438</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="24">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>#Không thể bàn cãi</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>350</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D28" s="21"/>
+      <c r="E28" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F28" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G28" s="21" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6">
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="1:8" ht="28.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="22">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B29" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="22" t="str">
+        <f>"#" &amp; E29</f>
+        <v>#Nhà dân tộc học</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>441</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>442</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="22">
+        <v>2</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="22" t="str">
+        <f t="shared" ref="D30:D50" si="1">"#" &amp; E30</f>
+        <v>#Bức tượng</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>445</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>446</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="1:8" ht="28.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="22">
+        <v>3</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Thuộc di truyền</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>449</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>450</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" ht="28.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="22">
+        <v>4</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Văn hóa dân gian</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>454</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>455</v>
+      </c>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="1:8" ht="28.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="22">
+        <v>5</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>456</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Gầy gò/Khẳng khiu</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>457</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="G33" s="22" t="s">
+        <v>459</v>
+      </c>
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8" ht="28.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="22">
+        <v>6</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Phấn hoa</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>461</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="22">
+        <v>7</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>464</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Trầm tích/Cặn</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>466</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="22">
+        <v>8</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Cây cọ/Cây dừa</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>469</v>
+      </c>
+      <c r="F36" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="22">
+        <v>9</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Xuất thân/Bắt nguồn</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>473</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="G37" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8" ht="28.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="22">
+        <v>10</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>476</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Tục ăn thịt người</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>477</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="G38" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="22">
+        <v>11</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Các thủ lĩnh đối địch</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="G39" s="22" t="s">
+        <v>483</v>
+      </c>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" ht="28.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="22">
+        <v>12</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>484</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Xe trượt</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>485</v>
+      </c>
+      <c r="F40" s="22" t="s">
+        <v>486</v>
+      </c>
+      <c r="G40" s="22" t="s">
+        <v>487</v>
+      </c>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8" ht="28.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="22">
+        <v>13</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>488</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Kéo mạnh/Vận chuyển</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>490</v>
+      </c>
+      <c r="G41" s="22" t="s">
+        <v>491</v>
+      </c>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="22">
+        <v>14</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>492</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Làm đổ/Lật đổ</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="F42" s="22" t="s">
+        <v>494</v>
+      </c>
+      <c r="G42" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="22">
+        <v>15</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>496</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Bị gió quật mạnh</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>498</v>
+      </c>
+      <c r="G43" s="22" t="s">
+        <v>499</v>
+      </c>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="22">
+        <v>16</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>500</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Cánh đồng cằn cỗi</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="F44" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="G44" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="22">
+        <v>17</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>504</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Vòng đá/Đá tròn</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="F45" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="G45" s="22" t="s">
+        <v>507</v>
+      </c>
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="1:8" ht="28.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="22">
+        <v>18</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>508</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Cho rằng/Tranh luận</v>
+      </c>
+      <c r="E46" s="22" t="s">
+        <v>509</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="G46" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="22">
+        <v>19</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>512</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Người định cư</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="F47" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="G47" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8" ht="28.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="22">
         <v>20</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="B48" s="21" t="s">
+        <v>516</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Sự miễn dịch</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>517</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>518</v>
+      </c>
+      <c r="G48" s="22" t="s">
+        <v>519</v>
+      </c>
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8" ht="28.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="22">
+        <v>21</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>520</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Tàn sát/Hủy diệt</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>521</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>522</v>
+      </c>
+      <c r="G49" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8" ht="28.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="22">
+        <v>22</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>524</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>#Co lại/Héo hon</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>525</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="G50" s="22" t="s">
+        <v>527</v>
+      </c>
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3"/>
+    </row>
+    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="24">
+        <v>1</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>528</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="24" t="str">
+        <f>"#" &amp; E53</f>
+        <v>#Mỹ học thần kinh</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>529</v>
+      </c>
+      <c r="F53" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="G53" s="24" t="s">
+        <v>533</v>
+      </c>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="24">
+        <v>2</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>530</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="24" t="str">
+        <f t="shared" ref="D54:D70" si="2">"#" &amp; E54</f>
+        <v>#Hạch hạnh nhân</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>531</v>
+      </c>
+      <c r="F54" s="24" t="s">
+        <v>534</v>
+      </c>
+      <c r="G54" s="24" t="s">
+        <v>535</v>
+      </c>
+      <c r="H54" s="3"/>
+    </row>
+    <row r="55" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="24">
+        <v>3</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>536</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Thuộc hình học</v>
+      </c>
+      <c r="E55" s="24" t="s">
+        <v>537</v>
+      </c>
+      <c r="F55" s="24" t="s">
+        <v>538</v>
+      </c>
+      <c r="G55" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="24">
+        <v>4</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>540</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Ngẫu nhiên/Bừa bãi</v>
+      </c>
+      <c r="E56" s="24" t="s">
+        <v>541</v>
+      </c>
+      <c r="F56" s="24" t="s">
+        <v>542</v>
+      </c>
+      <c r="G56" s="24" t="s">
+        <v>543</v>
+      </c>
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="24">
+        <v>5</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>544</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Khuynh hướng</v>
+      </c>
+      <c r="E57" s="24" t="s">
+        <v>545</v>
+      </c>
+      <c r="F57" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="G57" s="24" t="s">
+        <v>547</v>
+      </c>
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="24">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="B58" s="23" t="s">
+        <v>548</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Nét vẽ nguệch ngoạc</v>
+      </c>
+      <c r="E58" s="24" t="s">
+        <v>549</v>
+      </c>
+      <c r="F58" s="24" t="s">
+        <v>550</v>
+      </c>
+      <c r="G58" s="24" t="s">
+        <v>551</v>
+      </c>
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="24">
+        <v>7</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>552</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Con tinh tinh</v>
+      </c>
+      <c r="E59" s="24" t="s">
+        <v>553</v>
+      </c>
+      <c r="F59" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="G59" s="24" t="s">
+        <v>555</v>
+      </c>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="24">
+        <v>8</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>556</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Nét cọ lộn xộn</v>
+      </c>
+      <c r="E60" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="F60" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="G60" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="24">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B61" s="23" t="s">
+        <v>560</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Miêu tả thực tế</v>
+      </c>
+      <c r="E61" s="24" t="s">
+        <v>561</v>
+      </c>
+      <c r="F61" s="24" t="s">
+        <v>562</v>
+      </c>
+      <c r="G61" s="24" t="s">
+        <v>563</v>
+      </c>
+      <c r="H61" s="3"/>
+    </row>
+    <row r="62" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="24">
+        <v>10</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>564</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Giải mã/Hiểu</v>
+      </c>
+      <c r="E62" s="24" t="s">
+        <v>565</v>
+      </c>
+      <c r="F62" s="24" t="s">
+        <v>566</v>
+      </c>
+      <c r="G62" s="24" t="s">
+        <v>567</v>
+      </c>
+      <c r="H62" s="3"/>
+    </row>
+    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="24">
+        <v>11</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>568</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Bố cục tỉ mỉ</v>
+      </c>
+      <c r="E63" s="24" t="s">
+        <v>569</v>
+      </c>
+      <c r="F63" s="24" t="s">
+        <v>570</v>
+      </c>
+      <c r="G63" s="24" t="s">
+        <v>571</v>
+      </c>
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="24">
+        <v>12</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>572</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Lướt qua/Vụt qua</v>
+      </c>
+      <c r="E64" s="24" t="s">
+        <v>573</v>
+      </c>
+      <c r="F64" s="24" t="s">
+        <v>574</v>
+      </c>
+      <c r="G64" s="24" t="s">
+        <v>575</v>
+      </c>
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="24">
+        <v>13</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="C65" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="D65" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Sự giải thích/Diễn giải</v>
+      </c>
+      <c r="E65" s="24" t="s">
+        <v>577</v>
+      </c>
+      <c r="F65" s="24" t="s">
+        <v>578</v>
+      </c>
+      <c r="G65" s="24" t="s">
+        <v>579</v>
+      </c>
+      <c r="H65" s="3"/>
+    </row>
+    <row r="66" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="24">
+        <v>14</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>580</v>
+      </c>
+      <c r="C66" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="D66" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Sự phức tạp/Tỉ mỉ</v>
+      </c>
+      <c r="E66" s="24" t="s">
+        <v>581</v>
+      </c>
+      <c r="F66" s="24" t="s">
+        <v>582</v>
+      </c>
+      <c r="G66" s="24" t="s">
+        <v>583</v>
+      </c>
+      <c r="H66" s="3"/>
+    </row>
+    <row r="67" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="24">
+        <v>15</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>584</v>
+      </c>
+      <c r="C67" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Quá tải nhận thức</v>
+      </c>
+      <c r="E67" s="24" t="s">
+        <v>585</v>
+      </c>
+      <c r="F67" s="24" t="s">
+        <v>586</v>
+      </c>
+      <c r="G67" s="24" t="s">
+        <v>587</v>
+      </c>
+      <c r="H67" s="3"/>
+    </row>
+    <row r="68" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="24">
+        <v>16</v>
+      </c>
+      <c r="B68" s="23" t="s">
+        <v>588</v>
+      </c>
+      <c r="C68" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Phân hình</v>
+      </c>
+      <c r="E68" s="24" t="s">
+        <v>589</v>
+      </c>
+      <c r="F68" s="24" t="s">
+        <v>590</v>
+      </c>
+      <c r="G68" s="24" t="s">
+        <v>591</v>
+      </c>
+      <c r="H68" s="3"/>
+    </row>
+    <row r="69" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="24">
+        <v>17</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>592</v>
+      </c>
+      <c r="C69" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Họa tiết/Chủ đề</v>
+      </c>
+      <c r="E69" s="24" t="s">
+        <v>593</v>
+      </c>
+      <c r="F69" s="24" t="s">
+        <v>594</v>
+      </c>
+      <c r="G69" s="24" t="s">
+        <v>595</v>
+      </c>
+      <c r="H69" s="3"/>
+    </row>
+    <row r="70" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="24">
+        <v>18</v>
+      </c>
+      <c r="B70" s="23" t="s">
+        <v>596</v>
+      </c>
+      <c r="C70" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6">
-        <v>9</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6">
-        <v>12</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6">
-        <v>14</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="6">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="6">
-        <v>16</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="6">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="6">
-        <v>18</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="6">
-        <v>19</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="6">
-        <v>20</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="6">
-        <v>21</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="6">
-        <v>22</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="6">
-        <v>23</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="6">
-        <v>24</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="6">
-        <v>25</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="6">
-        <v>26</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="6">
-        <v>27</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="6">
-        <v>28</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="6">
-        <v>29</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="6">
-        <v>30</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="6">
-        <v>31</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="6">
-        <v>32</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="6">
-        <v>33</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="6">
-        <v>34</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="6">
-        <v>35</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="6">
-        <v>36</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>156</v>
-      </c>
+      <c r="D70" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>#Nán lại/Đọng lại</v>
+      </c>
+      <c r="E70" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="F70" s="24" t="s">
+        <v>598</v>
+      </c>
+      <c r="G70" s="24" t="s">
+        <v>599</v>
+      </c>
+      <c r="H70" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
